--- a/tests/fixtures/04_bank_statement/04_bank_statement_pattern-from-claude.xlsx
+++ b/tests/fixtures/04_bank_statement/04_bank_statement_pattern-from-claude.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -900,34 +900,39 @@
       <c r="G18" s="3" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>lbl:</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>col_totals</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>START:</t>
         </is>
       </c>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="4" t="n"/>
-      <c r="G19" s="4" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>cell:next</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>account_holder_label</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -937,7 +942,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>account.holder</t>
+          <t>account_holder_label</t>
         </is>
       </c>
       <c r="C21" s="5" t="n"/>
@@ -954,7 +959,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>account_number_label</t>
+          <t>account.holder</t>
         </is>
       </c>
       <c r="C22" s="5" t="n"/>
@@ -971,7 +976,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>account.number</t>
+          <t>account_number_label</t>
         </is>
       </c>
       <c r="C23" s="5" t="n"/>
@@ -988,7 +993,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>statement_period_label</t>
+          <t>account.number</t>
         </is>
       </c>
       <c r="C24" s="5" t="n"/>
@@ -1005,7 +1010,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>account.period</t>
+          <t>statement_period_label</t>
         </is>
       </c>
       <c r="C25" s="5" t="n"/>
@@ -1015,96 +1020,146 @@
       <c r="G25" s="5" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>account.period</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>table:*</t>
         </is>
       </c>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="6" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n"/>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+      <c r="G27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n"/>
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>HEADER:1</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>col_date</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>col_description</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>col_debit</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>col_credit</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>col_balance</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="3" t="n"/>
-      <c r="B28" s="3" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="3" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>DATA:*</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>transaction.date</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>transaction.description</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>transaction.debit</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>transaction.credit</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>transaction.balance</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>FOOTER:1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>col_totals</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>END:</t>
         </is>
       </c>
-      <c r="B29" s="4" t="n"/>
-      <c r="C29" s="4" t="n"/>
-      <c r="D29" s="4" t="n"/>
-      <c r="E29" s="4" t="n"/>
-      <c r="F29" s="4" t="n"/>
-      <c r="G29" s="4" t="n"/>
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
